--- a/artfynd/S 7863-2021 artfynd.xlsx
+++ b/artfynd/S 7863-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109473532</t>
         </is>
       </c>
     </row>
@@ -878,6 +888,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204165</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204178</t>
         </is>
       </c>
     </row>
@@ -1084,6 +1104,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204161</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204164</t>
         </is>
       </c>
     </row>
@@ -1302,6 +1332,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204152</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204158</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109473535</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109473536</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109473534</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109473375</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109473383</t>
         </is>
       </c>
     </row>
@@ -2012,6 +2077,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204142</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,8 +2187,29 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112204136</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>